--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
+++ b/314e-ig/output/ValueSet-time-accuracy-units-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
